--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484333_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484333_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9974</v>
+        <v>5.6511</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9977</v>
+        <v>4.8966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>7.4307</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3675</v>
+        <v>0.0213</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2337</v>
+        <v>-0.3349</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.3561</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6056</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6408</v>
+        <v>2.9114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1081</v>
+        <v>0.2698</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5327</v>
+        <v>2.6417</v>
       </c>
       <c r="G3" t="n">
         <v>1.5639</v>
@@ -688,13 +688,13 @@
         <v>3.3208</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2905</v>
+        <v>-0.0199</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3961</v>
+        <v>-0.2345</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1056</v>
+        <v>0.2145</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5045</v>
+        <v>2.5184</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9569</v>
+        <v>1.9164</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5476</v>
+        <v>0.6021</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7365</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2196</v>
+        <v>-0.2057</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2805</v>
+        <v>-0.3211</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0609</v>
+        <v>0.1154</v>
       </c>
       <c r="V4" t="n">
         <v>4.2652</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5061</v>
+        <v>1.755</v>
       </c>
       <c r="E5" t="n">
-        <v>2.015</v>
+        <v>2.3184</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.509</v>
+        <v>-0.5634</v>
       </c>
       <c r="G5" t="n">
         <v>0.4937</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5151</v>
+        <v>-0.2662</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.544</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3322</v>
+        <v>0.2778</v>
       </c>
       <c r="V5" t="n">
         <v>0.9414</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8859</v>
+        <v>1.2576</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8134</v>
+        <v>1.0711</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9275</v>
+        <v>0.1865</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5289</v>
+        <v>1.078</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3093</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5926</v>
+        <v>0.7687</v>
       </c>
       <c r="J6" t="n">
-        <v>1.393</v>
+        <v>1.1577</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9852</v>
+        <v>0.3888</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.7688</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9219</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9215</v>
+        <v>-0.0795</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4381</v>
+        <v>-0.4732</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1432</v>
+        <v>-0.0866</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2949</v>
+        <v>-0.3866</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8587</v>
+        <v>0.9754</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8083</v>
+        <v>1.7123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0504</v>
+        <v>-0.7368</v>
       </c>
       <c r="G7" t="n">
-        <v>1.078</v>
+        <v>-0.5289</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3093</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7687</v>
+        <v>-0.5926</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1577</v>
+        <v>1.393</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3888</v>
+        <v>1.9852</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7688</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-1.9219</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0795</v>
+        <v>-1.9215</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8722</v>
+        <v>0.5276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3494</v>
+        <v>0.0421</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5228</v>
+        <v>0.4855</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8155</v>
+        <v>0.7865</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8345</v>
+        <v>-0.6728</v>
       </c>
       <c r="F8" t="n">
-        <v>1.65</v>
+        <v>1.4593</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3229</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1617</v>
+        <v>0.1327</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>-0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4038</v>
+        <v>0.2132</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1957</v>
+        <v>0.0484</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0035</v>
+        <v>-1.969</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1992</v>
+        <v>2.0174</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0247</v>
+        <v>1.7948</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8066</v>
+        <v>0.4863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7819</v>
+        <v>1.3085</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3494</v>
+        <v>2.0046</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.6958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>1.3087</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3247</v>
+        <v>-0.2097</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2144</v>
+        <v>-0.2095</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5391</v>
+        <v>-0.0002</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3208</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>1.013</v>
+        <v>0.4024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0221</v>
+        <v>-0.0667</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9909</v>
+        <v>0.4691</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.029</v>
+        <v>-0.1639</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0701</v>
+        <v>-2.1452</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0991</v>
+        <v>1.9813</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7948</v>
+        <v>-0.0247</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4863</v>
+        <v>-0.8066</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3085</v>
+        <v>0.7819</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0046</v>
+        <v>-0.3494</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6958</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3087</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2097</v>
+        <v>0.3247</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2095</v>
+        <v>-0.2144</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0002</v>
+        <v>0.5391</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="S10" t="n">
-        <v>0.383</v>
+        <v>0.6534</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1678</v>
+        <v>-0.1196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5508</v>
+        <v>0.773</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3006</v>
+        <v>-0.7595</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3713</v>
+        <v>-1.7758</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0707</v>
+        <v>1.0163</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0689</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9404</v>
+        <v>0.4815</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6411</v>
+        <v>0.2367</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2993</v>
+        <v>0.2448</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.449</v>
+        <v>-1.2039</v>
       </c>
       <c r="E12" t="n">
         <v>-0.5810999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8679</v>
+        <v>-0.6228</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0281</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9949</v>
+        <v>-0.7498</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3494</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6455</v>
+        <v>-0.4004</v>
       </c>
       <c r="V12" t="n">
         <v>0.9414</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7297</v>
+        <v>-1.5196</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0131</v>
+        <v>-1.912</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2834</v>
+        <v>0.3924</v>
       </c>
       <c r="G13" t="n">
         <v>0.0472</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1089</v>
+        <v>0.1011</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0726</v>
+        <v>0.1816</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8865</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.9543</v>
+        <v>12.2569</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8258</v>
+        <v>3.128699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9.128299999999999</v>
+        <v>9.128500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>9.698300000000001</v>
@@ -1546,10 +1546,10 @@
         <v>22.4644</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3024999999999999</v>
+        <v>0.6052</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2415</v>
+        <v>-1.939</v>
       </c>
       <c r="U14" t="n">
         <v>2.544</v>
@@ -1558,7 +1558,7 @@
         <v>1.110223024625157e-16</v>
       </c>
       <c r="W14" t="n">
-        <v>6.869900000000001</v>
+        <v>6.869899999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.869899999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>1.654</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2126</v>
+        <v>2.5885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5374</v>
+        <v>-0.9345</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1378</v>
+        <v>0.5034</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0095</v>
+        <v>2.9182</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.8717</v>
+        <v>-2.4147</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1811</v>
+        <v>3.5557</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0289</v>
+        <v>3.5418</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8478</v>
+        <v>0.0138</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0433</v>
+        <v>-3.0522</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0194</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0239</v>
+        <v>-2.4285</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8308</v>
+        <v>-0.5406</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2337</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0646</v>
+        <v>0.2462</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.492</v>
+        <v>1.4595</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5885</v>
+        <v>2.2348</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0966</v>
+        <v>-0.7753</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5034</v>
+        <v>0.5927</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9182</v>
+        <v>1.902</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4147</v>
+        <v>-1.3093</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5557</v>
+        <v>2.4362</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5418</v>
+        <v>2.3958</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0138</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0522</v>
+        <v>-1.8435</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>-0.4937</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4285</v>
+        <v>-1.3498</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
         <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7027</v>
+        <v>0.0268</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3885</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.4153</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4959</v>
+        <v>-0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7731</v>
+        <v>1.1638</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7932</v>
+        <v>1.1393</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7292</v>
+        <v>1.0104</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.1289</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5927</v>
+        <v>0.1378</v>
       </c>
       <c r="H17" t="n">
-        <v>1.902</v>
+        <v>3.0095</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3093</v>
+        <v>-2.8717</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4362</v>
+        <v>2.1811</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3958</v>
+        <v>3.0289</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-0.8478</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8435</v>
+        <v>-2.0433</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4937</v>
+        <v>-0.0194</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3498</v>
+        <v>-2.0239</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6395</v>
+        <v>0.2201</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8941</v>
+        <v>-0.436</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2546</v>
+        <v>0.656</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1638</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3571</v>
+        <v>0.7084</v>
       </c>
       <c r="E18" t="n">
         <v>0.4474</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0394</v>
@@ -1858,13 +1858,13 @@
         <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0528</v>
+        <v>0.2985</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2337</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1809</v>
+        <v>0.5323</v>
       </c>
       <c r="V18" t="n">
         <v>0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3069</v>
+        <v>0.4158</v>
       </c>
       <c r="E19" t="n">
         <v>-1.1979</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5048</v>
+        <v>1.6138</v>
       </c>
       <c r="G19" t="n">
         <v>0.1462</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.23</v>
+        <v>-0.121</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0726</v>
+        <v>0.1816</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4669</v>
+        <v>-0.9134</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8876</v>
+        <v>-1.6853</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4206</v>
+        <v>0.772</v>
       </c>
       <c r="G20" t="n">
         <v>0.284</v>
@@ -2014,13 +2014,13 @@
         <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5316</v>
+        <v>0.022</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4099</v>
+        <v>-0.2077</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1217</v>
+        <v>0.2297</v>
       </c>
       <c r="V20" t="n">
         <v>2.4921</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8466</v>
+        <v>-2.2487</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0394</v>
+        <v>-2.0713</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8072</v>
+        <v>-0.1774</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4202</v>
+        <v>-0.3299</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3973</v>
+        <v>0.7222</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0229</v>
+        <v>-1.0521</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2663</v>
+        <v>2.1229</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0819</v>
+        <v>0.8813</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3482</v>
+        <v>1.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1538</v>
+        <v>-2.4528</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4792</v>
+        <v>-0.1591</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6747</v>
+        <v>-2.2937</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>3.1255</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1364</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1804</v>
+        <v>-0.2874</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.044</v>
+        <v>0.3686</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3171</v>
+        <v>-3.4044</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.678</v>
+        <v>-2.8878</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.639</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3299</v>
+        <v>-1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7222</v>
+        <v>-1.3699</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0521</v>
+        <v>-0.5401</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1229</v>
+        <v>-0.5513</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8813</v>
+        <v>-0.5513</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2416</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4528</v>
+        <v>-1.3587</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1591</v>
+        <v>-0.8186</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2937</v>
+        <v>-0.5401</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9871</v>
+        <v>-0.4711</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8941</v>
+        <v>-0.3831</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0931</v>
+        <v>-0.0881</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7493</v>
+        <v>-3.5193</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9889</v>
+        <v>-2.8483</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7604</v>
+        <v>-0.671</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.91</v>
+        <v>-2.4202</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3699</v>
+        <v>-0.3973</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5401</v>
+        <v>-2.0229</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5513</v>
+        <v>-1.2663</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5513</v>
+        <v>0.0819</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.3482</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3587</v>
+        <v>-1.1538</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8186</v>
+        <v>-0.4792</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5401</v>
+        <v>-0.6747</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0.4636</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4842</v>
+        <v>0.3715</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3318</v>
+        <v>0.0921</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2738</v>
+        <v>-5.8975</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3144</v>
+        <v>-4.7189</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9593</v>
+        <v>-1.1786</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6631</v>
@@ -2326,13 +2326,13 @@
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6898</v>
+        <v>1.0661</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5147</v>
+        <v>0.1102</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1752</v>
+        <v>0.9559</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4959</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.9545</v>
+        <v>-10.6063</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.128499999999999</v>
+        <v>-9.128399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.826000000000001</v>
+        <v>-1.4777</v>
       </c>
       <c r="G25" t="n">
         <v>-9.698499999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>5.140799999999999</v>
+        <v>5.1408</v>
       </c>
       <c r="I25" t="n">
         <v>-14.8391</v>
@@ -2380,10 +2380,10 @@
         <v>9.01</v>
       </c>
       <c r="K25" t="n">
-        <v>9.006100000000002</v>
+        <v>9.0061</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003999999999999976</v>
+        <v>0.003999999999999823</v>
       </c>
       <c r="M25" t="n">
         <v>-18.7082</v>
@@ -2404,13 +2404,13 @@
         <v>20.5112</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3026999999999997</v>
+        <v>1.0456</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.544</v>
+        <v>-2.5441</v>
       </c>
       <c r="U25" t="n">
-        <v>2.241400000000001</v>
+        <v>3.5896</v>
       </c>
       <c r="V25" t="n">
         <v>2.220446049250313e-16</v>
@@ -2419,7 +2419,7 @@
         <v>6.869899999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.8699</v>
+        <v>-6.869899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484333_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484333_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1328,6 +1378,11 @@
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.869899999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,11 +2288,16 @@
       <c r="X22" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2264,6 +2370,11 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484333_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.869899999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
